--- a/data/file_generation/reference/data_67/A文件-物流公司费用数据分析_res.xlsx
+++ b/data/file_generation/reference/data_67/A文件-物流公司费用数据分析_res.xlsx
@@ -3131,26 +3131,18 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
+  <documentManagement/>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23D258BD-4BAE-4661-BFBA-5E445DE66A36}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6DFDAE3-1ACE-4A82-B2F5-763853BB3969}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD83FFEE-2166-44FA-A11D-483BA92E09EE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E7420BD-27E7-4BD6-9378-894F8B83C8B4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59DC3234-DB79-4BE2-8F9E-6E4F0B8275F3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4E69C63-3A73-4EB4-A052-6B781075D1ED}"/>
 </file>